--- a/INCREMENTO2/Excels/Grupo 6 - Organizacion Trabajo.xlsx
+++ b/INCREMENTO2/Excels/Grupo 6 - Organizacion Trabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addan\OneDrive\Documentos\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BDE7BC-EE21-43BB-8771-6194BFE5FFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F9BA01-CAAF-468D-B5AF-4A856DC7A8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,16 +311,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,12 +334,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -572,1917 +572,1917 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="6" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="6" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="6" t="s">
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="6" t="s">
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
     </row>
     <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
     </row>
     <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="8" t="s">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
     </row>
     <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8" t="s">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="8" t="s">
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
     </row>
     <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
     </row>
     <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8" t="s">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8" t="s">
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8" t="s">
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="8" t="s">
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6" t="s">
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
     </row>
     <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="8" t="s">
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="8" t="s">
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="6" t="s">
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="6"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
     </row>
     <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
     </row>
     <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9"/>
     </row>
     <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8" t="s">
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
     </row>
     <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
     </row>
     <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
     </row>
     <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10" t="s">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
     </row>
     <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="3" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="2" t="s">
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="3" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="2" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="3" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="2" t="s">
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
     </row>
     <row r="31" spans="1:30" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="3" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="2" t="s">
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2" t="s">
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="3" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="2" t="s">
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="3" t="s">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="2" t="s">
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2" t="s">
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="3" t="s">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="2" t="s">
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2" t="s">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="3" t="s">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="2" t="s">
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2" t="s">
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="3" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="2" t="s">
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2" t="s">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="3" t="s">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="2" t="s">
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2" t="s">
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2" t="s">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="3" t="s">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3" t="s">
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="2" t="s">
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="3" t="s">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3" t="s">
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="2" t="s">
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="3" t="s">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3" t="s">
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="2" t="s">
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
     </row>
     <row r="53" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="3" t="s">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3" t="s">
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="2" t="s">
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10" t="s">
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10" t="s">
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10" t="s">
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="3" t="s">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3" t="s">
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="2" t="s">
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="3" t="s">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="2" t="s">
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2" t="s">
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3" t="s">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="2" t="s">
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="3" t="s">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="2" t="s">
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2" t="s">
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="3" t="s">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="2" t="s">
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2" t="s">
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="3" t="s">
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="2" t="s">
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2" t="s">
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="3" t="s">
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="2" t="s">
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2" t="s">
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="3" t="s">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="2" t="s">
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2" t="s">
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="3" t="s">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="2" t="s">
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2" t="s">
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="3" t="s">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="2" t="s">
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2" t="s">
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="2" t="s">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2" t="s">
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2" t="s">
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="3" t="s">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3" t="s">
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="2" t="s">
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="3" t="s">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3" t="s">
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="2" t="s">
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="3" t="s">
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="2" t="s">
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
     </row>
     <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="3" t="s">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="2" t="s">
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3406,132 +3406,94 @@
     <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="238">
-    <mergeCell ref="A87:C88"/>
-    <mergeCell ref="D87:F88"/>
-    <mergeCell ref="G87:I88"/>
-    <mergeCell ref="J87:L88"/>
-    <mergeCell ref="A81:C82"/>
-    <mergeCell ref="D81:F82"/>
-    <mergeCell ref="G81:I82"/>
-    <mergeCell ref="J81:L82"/>
-    <mergeCell ref="A83:C84"/>
-    <mergeCell ref="D83:F84"/>
-    <mergeCell ref="G83:I84"/>
-    <mergeCell ref="J83:L84"/>
-    <mergeCell ref="A85:C86"/>
-    <mergeCell ref="D85:F86"/>
-    <mergeCell ref="G85:I86"/>
-    <mergeCell ref="J85:L86"/>
-    <mergeCell ref="A75:C76"/>
-    <mergeCell ref="D75:F76"/>
-    <mergeCell ref="G75:I76"/>
-    <mergeCell ref="J75:L76"/>
-    <mergeCell ref="A77:C78"/>
-    <mergeCell ref="D77:F78"/>
-    <mergeCell ref="G77:I78"/>
-    <mergeCell ref="J77:L78"/>
-    <mergeCell ref="A79:C80"/>
-    <mergeCell ref="D79:F80"/>
-    <mergeCell ref="G79:I80"/>
-    <mergeCell ref="J79:L80"/>
-    <mergeCell ref="A69:C70"/>
-    <mergeCell ref="D69:F70"/>
-    <mergeCell ref="G69:I70"/>
-    <mergeCell ref="J69:L70"/>
-    <mergeCell ref="A71:C72"/>
-    <mergeCell ref="D71:F72"/>
-    <mergeCell ref="G71:I72"/>
-    <mergeCell ref="J71:L72"/>
-    <mergeCell ref="A73:C74"/>
-    <mergeCell ref="D73:F74"/>
-    <mergeCell ref="G73:I74"/>
-    <mergeCell ref="J73:L74"/>
-    <mergeCell ref="A63:C64"/>
-    <mergeCell ref="D63:F64"/>
-    <mergeCell ref="G63:I64"/>
-    <mergeCell ref="J63:L64"/>
-    <mergeCell ref="A65:C66"/>
-    <mergeCell ref="D65:F66"/>
-    <mergeCell ref="G65:I66"/>
-    <mergeCell ref="J65:L66"/>
-    <mergeCell ref="A67:C68"/>
-    <mergeCell ref="D67:F68"/>
-    <mergeCell ref="G67:I68"/>
-    <mergeCell ref="J67:L68"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="J58:L58"/>
-    <mergeCell ref="A59:C60"/>
-    <mergeCell ref="D59:F60"/>
-    <mergeCell ref="G59:I60"/>
-    <mergeCell ref="J59:L60"/>
-    <mergeCell ref="A61:C62"/>
-    <mergeCell ref="D61:F62"/>
-    <mergeCell ref="G61:I62"/>
-    <mergeCell ref="J61:L62"/>
-    <mergeCell ref="V15:X16"/>
-    <mergeCell ref="Y15:AA16"/>
-    <mergeCell ref="AB15:AD16"/>
-    <mergeCell ref="A15:C16"/>
-    <mergeCell ref="D15:F16"/>
-    <mergeCell ref="G15:I16"/>
-    <mergeCell ref="J15:L16"/>
-    <mergeCell ref="M15:O16"/>
-    <mergeCell ref="P15:R16"/>
-    <mergeCell ref="S15:U16"/>
-    <mergeCell ref="V5:X6"/>
-    <mergeCell ref="Y5:AA6"/>
-    <mergeCell ref="AB5:AD6"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:F6"/>
-    <mergeCell ref="G5:I6"/>
-    <mergeCell ref="J5:L6"/>
-    <mergeCell ref="M5:O6"/>
-    <mergeCell ref="P5:R6"/>
-    <mergeCell ref="S5:U6"/>
-    <mergeCell ref="V3:X4"/>
-    <mergeCell ref="Y3:AA4"/>
-    <mergeCell ref="AB3:AD4"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="D3:F4"/>
-    <mergeCell ref="G3:I4"/>
-    <mergeCell ref="J3:L4"/>
-    <mergeCell ref="M3:O4"/>
-    <mergeCell ref="P3:R4"/>
-    <mergeCell ref="S3:U4"/>
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="Y1:AA2"/>
-    <mergeCell ref="AB1:AD2"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:F2"/>
-    <mergeCell ref="G1:I2"/>
-    <mergeCell ref="J1:L2"/>
-    <mergeCell ref="M1:O2"/>
-    <mergeCell ref="P1:R2"/>
-    <mergeCell ref="S1:U2"/>
-    <mergeCell ref="V13:X14"/>
-    <mergeCell ref="Y13:AA14"/>
-    <mergeCell ref="AB13:AD14"/>
-    <mergeCell ref="A13:C14"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:I14"/>
-    <mergeCell ref="J13:L14"/>
-    <mergeCell ref="M13:O14"/>
-    <mergeCell ref="P13:R14"/>
-    <mergeCell ref="S13:U14"/>
-    <mergeCell ref="P9:R10"/>
-    <mergeCell ref="S9:U10"/>
-    <mergeCell ref="V11:X12"/>
-    <mergeCell ref="Y11:AA12"/>
-    <mergeCell ref="AB11:AD12"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:I12"/>
-    <mergeCell ref="J11:L12"/>
-    <mergeCell ref="M11:O12"/>
-    <mergeCell ref="P11:R12"/>
-    <mergeCell ref="S11:U12"/>
+    <mergeCell ref="J54:L55"/>
+    <mergeCell ref="D48:F49"/>
+    <mergeCell ref="G48:I49"/>
+    <mergeCell ref="J48:L49"/>
+    <mergeCell ref="D50:F51"/>
+    <mergeCell ref="G50:I51"/>
+    <mergeCell ref="J50:L51"/>
+    <mergeCell ref="A52:C53"/>
+    <mergeCell ref="D52:F53"/>
+    <mergeCell ref="G52:I53"/>
+    <mergeCell ref="J52:L53"/>
+    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="D32:F33"/>
+    <mergeCell ref="G32:I33"/>
+    <mergeCell ref="D34:F35"/>
+    <mergeCell ref="G34:I35"/>
+    <mergeCell ref="D36:F37"/>
+    <mergeCell ref="G36:I37"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:I39"/>
+    <mergeCell ref="D40:F41"/>
+    <mergeCell ref="G40:I41"/>
+    <mergeCell ref="D42:F43"/>
+    <mergeCell ref="G42:I43"/>
+    <mergeCell ref="D44:F45"/>
+    <mergeCell ref="D54:F55"/>
+    <mergeCell ref="G54:I55"/>
+    <mergeCell ref="AB17:AD18"/>
+    <mergeCell ref="AB19:AD20"/>
+    <mergeCell ref="AB21:AD22"/>
+    <mergeCell ref="A48:C49"/>
+    <mergeCell ref="A50:C51"/>
+    <mergeCell ref="J32:L33"/>
+    <mergeCell ref="J34:L35"/>
+    <mergeCell ref="J36:L37"/>
+    <mergeCell ref="J38:L39"/>
+    <mergeCell ref="J40:L41"/>
+    <mergeCell ref="J42:L43"/>
+    <mergeCell ref="G44:I45"/>
+    <mergeCell ref="J44:L45"/>
+    <mergeCell ref="D46:F47"/>
+    <mergeCell ref="G46:I47"/>
+    <mergeCell ref="J46:L47"/>
+    <mergeCell ref="V17:X18"/>
+    <mergeCell ref="V19:X20"/>
+    <mergeCell ref="V21:X22"/>
+    <mergeCell ref="Y17:AA18"/>
+    <mergeCell ref="Y19:AA20"/>
+    <mergeCell ref="Y21:AA22"/>
+    <mergeCell ref="P17:R18"/>
+    <mergeCell ref="P19:R20"/>
+    <mergeCell ref="P21:R22"/>
+    <mergeCell ref="S17:U18"/>
+    <mergeCell ref="S19:U20"/>
+    <mergeCell ref="S21:U22"/>
+    <mergeCell ref="J17:L18"/>
+    <mergeCell ref="J19:L20"/>
+    <mergeCell ref="J21:L22"/>
+    <mergeCell ref="M17:O18"/>
+    <mergeCell ref="M19:O20"/>
+    <mergeCell ref="M21:O22"/>
+    <mergeCell ref="D17:F18"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="D21:F22"/>
+    <mergeCell ref="G17:I18"/>
+    <mergeCell ref="G19:I20"/>
+    <mergeCell ref="G21:I22"/>
+    <mergeCell ref="A42:C43"/>
+    <mergeCell ref="A44:C45"/>
+    <mergeCell ref="A46:C47"/>
+    <mergeCell ref="A17:C18"/>
+    <mergeCell ref="A21:C22"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="A34:C35"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A28:C29"/>
+    <mergeCell ref="A19:C20"/>
+    <mergeCell ref="G26:I27"/>
+    <mergeCell ref="J26:L27"/>
+    <mergeCell ref="A30:C31"/>
+    <mergeCell ref="D28:F29"/>
+    <mergeCell ref="G28:I29"/>
+    <mergeCell ref="J28:L29"/>
+    <mergeCell ref="D30:F31"/>
+    <mergeCell ref="G30:I31"/>
+    <mergeCell ref="J30:L31"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="J25:L25"/>
@@ -3556,94 +3518,132 @@
     <mergeCell ref="G9:I10"/>
     <mergeCell ref="J9:L10"/>
     <mergeCell ref="M9:O10"/>
-    <mergeCell ref="G26:I27"/>
-    <mergeCell ref="J26:L27"/>
-    <mergeCell ref="A30:C31"/>
-    <mergeCell ref="D28:F29"/>
-    <mergeCell ref="G28:I29"/>
-    <mergeCell ref="J28:L29"/>
-    <mergeCell ref="D30:F31"/>
-    <mergeCell ref="G30:I31"/>
-    <mergeCell ref="J30:L31"/>
-    <mergeCell ref="A42:C43"/>
-    <mergeCell ref="A44:C45"/>
-    <mergeCell ref="A46:C47"/>
-    <mergeCell ref="A17:C18"/>
-    <mergeCell ref="A21:C22"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="A34:C35"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="A28:C29"/>
-    <mergeCell ref="A19:C20"/>
-    <mergeCell ref="J17:L18"/>
-    <mergeCell ref="J19:L20"/>
-    <mergeCell ref="J21:L22"/>
-    <mergeCell ref="M17:O18"/>
-    <mergeCell ref="M19:O20"/>
-    <mergeCell ref="M21:O22"/>
-    <mergeCell ref="D17:F18"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="G17:I18"/>
-    <mergeCell ref="G19:I20"/>
-    <mergeCell ref="G21:I22"/>
-    <mergeCell ref="Y17:AA18"/>
-    <mergeCell ref="Y19:AA20"/>
-    <mergeCell ref="Y21:AA22"/>
-    <mergeCell ref="P17:R18"/>
-    <mergeCell ref="P19:R20"/>
-    <mergeCell ref="P21:R22"/>
-    <mergeCell ref="S17:U18"/>
-    <mergeCell ref="S19:U20"/>
-    <mergeCell ref="S21:U22"/>
-    <mergeCell ref="D42:F43"/>
-    <mergeCell ref="G42:I43"/>
-    <mergeCell ref="D44:F45"/>
-    <mergeCell ref="D54:F55"/>
-    <mergeCell ref="G54:I55"/>
-    <mergeCell ref="AB17:AD18"/>
-    <mergeCell ref="AB19:AD20"/>
-    <mergeCell ref="AB21:AD22"/>
-    <mergeCell ref="A48:C49"/>
-    <mergeCell ref="A50:C51"/>
-    <mergeCell ref="J32:L33"/>
-    <mergeCell ref="J34:L35"/>
-    <mergeCell ref="J36:L37"/>
-    <mergeCell ref="J38:L39"/>
-    <mergeCell ref="J40:L41"/>
-    <mergeCell ref="J42:L43"/>
-    <mergeCell ref="G44:I45"/>
-    <mergeCell ref="J44:L45"/>
-    <mergeCell ref="D46:F47"/>
-    <mergeCell ref="G46:I47"/>
-    <mergeCell ref="J46:L47"/>
-    <mergeCell ref="V17:X18"/>
-    <mergeCell ref="V19:X20"/>
-    <mergeCell ref="V21:X22"/>
-    <mergeCell ref="D32:F33"/>
-    <mergeCell ref="G32:I33"/>
-    <mergeCell ref="D34:F35"/>
-    <mergeCell ref="G34:I35"/>
-    <mergeCell ref="D36:F37"/>
-    <mergeCell ref="G36:I37"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:I39"/>
-    <mergeCell ref="D40:F41"/>
-    <mergeCell ref="G40:I41"/>
-    <mergeCell ref="J54:L55"/>
-    <mergeCell ref="D48:F49"/>
-    <mergeCell ref="G48:I49"/>
-    <mergeCell ref="J48:L49"/>
-    <mergeCell ref="D50:F51"/>
-    <mergeCell ref="G50:I51"/>
-    <mergeCell ref="J50:L51"/>
-    <mergeCell ref="A52:C53"/>
-    <mergeCell ref="D52:F53"/>
-    <mergeCell ref="G52:I53"/>
-    <mergeCell ref="J52:L53"/>
-    <mergeCell ref="A54:C55"/>
+    <mergeCell ref="P9:R10"/>
+    <mergeCell ref="S9:U10"/>
+    <mergeCell ref="V11:X12"/>
+    <mergeCell ref="Y11:AA12"/>
+    <mergeCell ref="AB11:AD12"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="G11:I12"/>
+    <mergeCell ref="J11:L12"/>
+    <mergeCell ref="M11:O12"/>
+    <mergeCell ref="P11:R12"/>
+    <mergeCell ref="S11:U12"/>
+    <mergeCell ref="V13:X14"/>
+    <mergeCell ref="Y13:AA14"/>
+    <mergeCell ref="AB13:AD14"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:I14"/>
+    <mergeCell ref="J13:L14"/>
+    <mergeCell ref="M13:O14"/>
+    <mergeCell ref="P13:R14"/>
+    <mergeCell ref="S13:U14"/>
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="Y1:AA2"/>
+    <mergeCell ref="AB1:AD2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:F2"/>
+    <mergeCell ref="G1:I2"/>
+    <mergeCell ref="J1:L2"/>
+    <mergeCell ref="M1:O2"/>
+    <mergeCell ref="P1:R2"/>
+    <mergeCell ref="S1:U2"/>
+    <mergeCell ref="V3:X4"/>
+    <mergeCell ref="Y3:AA4"/>
+    <mergeCell ref="AB3:AD4"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="D3:F4"/>
+    <mergeCell ref="G3:I4"/>
+    <mergeCell ref="J3:L4"/>
+    <mergeCell ref="M3:O4"/>
+    <mergeCell ref="P3:R4"/>
+    <mergeCell ref="S3:U4"/>
+    <mergeCell ref="V5:X6"/>
+    <mergeCell ref="Y5:AA6"/>
+    <mergeCell ref="AB5:AD6"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:F6"/>
+    <mergeCell ref="G5:I6"/>
+    <mergeCell ref="J5:L6"/>
+    <mergeCell ref="M5:O6"/>
+    <mergeCell ref="P5:R6"/>
+    <mergeCell ref="S5:U6"/>
+    <mergeCell ref="V15:X16"/>
+    <mergeCell ref="Y15:AA16"/>
+    <mergeCell ref="AB15:AD16"/>
+    <mergeCell ref="A15:C16"/>
+    <mergeCell ref="D15:F16"/>
+    <mergeCell ref="G15:I16"/>
+    <mergeCell ref="J15:L16"/>
+    <mergeCell ref="M15:O16"/>
+    <mergeCell ref="P15:R16"/>
+    <mergeCell ref="S15:U16"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="D59:F60"/>
+    <mergeCell ref="G59:I60"/>
+    <mergeCell ref="J59:L60"/>
+    <mergeCell ref="A61:C62"/>
+    <mergeCell ref="D61:F62"/>
+    <mergeCell ref="G61:I62"/>
+    <mergeCell ref="J61:L62"/>
+    <mergeCell ref="A63:C64"/>
+    <mergeCell ref="D63:F64"/>
+    <mergeCell ref="G63:I64"/>
+    <mergeCell ref="J63:L64"/>
+    <mergeCell ref="A65:C66"/>
+    <mergeCell ref="D65:F66"/>
+    <mergeCell ref="G65:I66"/>
+    <mergeCell ref="J65:L66"/>
+    <mergeCell ref="A67:C68"/>
+    <mergeCell ref="D67:F68"/>
+    <mergeCell ref="G67:I68"/>
+    <mergeCell ref="J67:L68"/>
+    <mergeCell ref="A69:C70"/>
+    <mergeCell ref="D69:F70"/>
+    <mergeCell ref="G69:I70"/>
+    <mergeCell ref="J69:L70"/>
+    <mergeCell ref="A71:C72"/>
+    <mergeCell ref="D71:F72"/>
+    <mergeCell ref="G71:I72"/>
+    <mergeCell ref="J71:L72"/>
+    <mergeCell ref="A73:C74"/>
+    <mergeCell ref="D73:F74"/>
+    <mergeCell ref="G73:I74"/>
+    <mergeCell ref="J73:L74"/>
+    <mergeCell ref="A75:C76"/>
+    <mergeCell ref="D75:F76"/>
+    <mergeCell ref="G75:I76"/>
+    <mergeCell ref="J75:L76"/>
+    <mergeCell ref="A77:C78"/>
+    <mergeCell ref="D77:F78"/>
+    <mergeCell ref="G77:I78"/>
+    <mergeCell ref="J77:L78"/>
+    <mergeCell ref="A79:C80"/>
+    <mergeCell ref="D79:F80"/>
+    <mergeCell ref="G79:I80"/>
+    <mergeCell ref="J79:L80"/>
+    <mergeCell ref="A87:C88"/>
+    <mergeCell ref="D87:F88"/>
+    <mergeCell ref="G87:I88"/>
+    <mergeCell ref="J87:L88"/>
+    <mergeCell ref="A81:C82"/>
+    <mergeCell ref="D81:F82"/>
+    <mergeCell ref="G81:I82"/>
+    <mergeCell ref="J81:L82"/>
+    <mergeCell ref="A83:C84"/>
+    <mergeCell ref="D83:F84"/>
+    <mergeCell ref="G83:I84"/>
+    <mergeCell ref="J83:L84"/>
+    <mergeCell ref="A85:C86"/>
+    <mergeCell ref="D85:F86"/>
+    <mergeCell ref="G85:I86"/>
+    <mergeCell ref="J85:L86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
